--- a/data/tefas.xlsx
+++ b/data/tefas.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>11.08.2026 15:26:34</t>
+    <t>11.08.2026 15:31:11</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
